--- a/data/trending_integrated_20261027_13.xlsx
+++ b/data/trending_integrated_20261027_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41934416310</v>
+        <v>41939402760</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18725939765</v>
+        <v>18727819665</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2210</v>
+        <v>20500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.60%</t>
+          <t>'+7.61%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="H4" t="n">
-        <v>4.89</v>
+        <v>0.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2035</v>
+        <v>19050</v>
       </c>
       <c r="K4" t="n">
-        <v>2035</v>
+        <v>19450</v>
       </c>
       <c r="L4" t="n">
-        <v>2300</v>
+        <v>22450</v>
       </c>
       <c r="M4" t="n">
-        <v>1953</v>
+        <v>18430</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>44726982897</v>
+        <v>67596430090</v>
       </c>
       <c r="P4" t="n">
-        <v>4980</v>
+        <v>62100</v>
       </c>
       <c r="Q4" t="n">
-        <v>749</v>
+        <v>14600</v>
       </c>
       <c r="R4" t="n">
-        <v>-89000</v>
+        <v>7000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>스마트 팩토리 및 공장 자동화 관련 기대감. 로봇 관련 전시회(로봇월드) 일정 언급. 주가 변동성 및 개미 털기 우려.</t>
+          <t>로봇 기업으로 분류. 기술적 분석상 양음 라인 형성 및 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['스마트팩토리', '로봇월드', '변동성']</t>
+          <t>['로봇', '기술적분석', '흑자기업']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20500</v>
+        <v>1358000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.61%</t>
+          <t>'+6.51%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>444</v>
       </c>
       <c r="G5" t="n">
-        <v>132</v>
+        <v>1607</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>48.66</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>19050</v>
+        <v>1275000</v>
       </c>
       <c r="K5" t="n">
-        <v>19450</v>
+        <v>1346000</v>
       </c>
       <c r="L5" t="n">
-        <v>22450</v>
+        <v>1381000</v>
       </c>
       <c r="M5" t="n">
-        <v>18430</v>
+        <v>1341000</v>
       </c>
       <c r="N5" t="n">
-        <v>0.18</v>
+        <v>48.69</v>
       </c>
       <c r="O5" t="n">
-        <v>67246269865</v>
+        <v>2559757294500</v>
       </c>
       <c r="P5" t="n">
-        <v>62100</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>14600</v>
+        <v>501000</v>
       </c>
       <c r="R5" t="n">
-        <v>7000</v>
+        <v>174000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇 기업 빅웨이브 언급과 함께 흑자 기업이라는 점은 긍정적이나, 피뢰침 현상 및 보호예수 물량 매도 우려 등 부정적 전망도 존재함. 단타 대회 언급 등 투기적 성향의 게시글 다수.</t>
+          <t>실적 발표 이후 주가 상승 기대. 외국인, 기관 쌍끌이 매수세 유입.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇주', '흑자기업', '단타']</t>
+          <t>['실적발표', '외국인기관', '주주환원']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1360000</v>
+        <v>2160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.67%</t>
+          <t>'+6.14%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>94</v>
       </c>
       <c r="F6" t="n">
-        <v>437</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>1587</v>
+        <v>164</v>
       </c>
       <c r="H6" t="n">
-        <v>48.66</v>
+        <v>4.89</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1275000</v>
+        <v>2035</v>
       </c>
       <c r="K6" t="n">
-        <v>1346000</v>
+        <v>2035</v>
       </c>
       <c r="L6" t="n">
-        <v>1381000</v>
+        <v>2300</v>
       </c>
       <c r="M6" t="n">
-        <v>1341000</v>
+        <v>1953</v>
       </c>
       <c r="N6" t="n">
-        <v>48.69</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>2540140976000</v>
+        <v>45348572023</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>4980</v>
       </c>
       <c r="Q6" t="n">
-        <v>501000</v>
+        <v>749</v>
       </c>
       <c r="R6" t="n">
-        <v>174000</v>
+        <v>-89000</v>
       </c>
       <c r="S6" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>실적 발표 이후 매수 의견과 함께 외국인, 기관의 쌍끌이 매수세에 대한 기대감이 있으나, 축제 끝, 힘 없다 등 부정적 언급도 존재함. 주주환원 발표 기대감은 긍정적 요인.</t>
+          <t>로봇 관련주로 분류. 변동성 속 종가 관리 움직임.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적 발표', '주주환원', '외국인 기관']</t>
+          <t>['로봇', '변동성', '종가관리']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>223000</v>
+        <v>222750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.69%</t>
+          <t>'+4.58%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G7" t="n">
-        <v>1304</v>
+        <v>1283</v>
       </c>
       <c r="H7" t="n">
         <v>46.1</v>
@@ -1070,7 +1070,7 @@
         <v>46.11</v>
       </c>
       <c r="O7" t="n">
-        <v>1827626386250</v>
+        <v>1838068831000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대통령 외교 논란 속 공매도 세력에 대한 언급과 함께 실적 및 주주환원 발표 기대감이 존재하나, 외인 매도세 및 SK하이닉스 ETF 퇴장 뉴스 등 부정적 요인이 혼재됨.</t>
+          <t>실적 및 주주환원 발표 기대감 속 외인 매도세 지속. 대외 변수 영향.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도', '실적 발표', '외인 매도']</t>
+          <t>['주주환원', '외인매도', '실적발표']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62300</v>
+        <v>62200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>91</v>
       </c>
       <c r="G8" t="n">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="H8" t="n">
         <v>40.44</v>
@@ -1162,7 +1162,7 @@
         <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>206821772250</v>
+        <v>213265368450</v>
       </c>
       <c r="P8" t="n">
         <v>67300</v>
@@ -1207,184 +1207,184 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13770</v>
+        <v>14650</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.91%</t>
+          <t>'+3.02%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>290</v>
+        <v>367</v>
       </c>
       <c r="H9" t="n">
-        <v>2.82</v>
+        <v>10.02</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13380</v>
+        <v>14220</v>
       </c>
       <c r="K9" t="n">
-        <v>14000</v>
+        <v>14390</v>
       </c>
       <c r="L9" t="n">
-        <v>14410</v>
+        <v>15150</v>
       </c>
       <c r="M9" t="n">
-        <v>13660</v>
+        <v>14390</v>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>10.03</v>
       </c>
       <c r="O9" t="n">
-        <v>55936603345</v>
+        <v>35501269150</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>1760</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-88000</v>
+        <v>392000</v>
       </c>
       <c r="S9" t="n">
-        <v>6000</v>
+        <v>30000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대한광통신, 유리기판 특허 관련 기대감. 미국 전력 및 통신/반도체 업황 언급.</t>
+          <t>영업이익 223% 증가 등 견조한 실적 발표. AI 수혜 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유리기판', '특허', '업황']</t>
+          <t>['영업이익', '실적발표', 'AI수혜']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14630</v>
+        <v>13740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.88%</t>
+          <t>'+2.69%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>354</v>
+        <v>298</v>
       </c>
       <c r="H10" t="n">
-        <v>10.02</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14220</v>
+        <v>13380</v>
       </c>
       <c r="K10" t="n">
-        <v>14390</v>
+        <v>14000</v>
       </c>
       <c r="L10" t="n">
-        <v>15150</v>
+        <v>14410</v>
       </c>
       <c r="M10" t="n">
-        <v>14390</v>
+        <v>13660</v>
       </c>
       <c r="N10" t="n">
-        <v>10.03</v>
+        <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>35175955125</v>
+        <v>56298579930</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>1760</v>
       </c>
       <c r="R10" t="n">
-        <v>392000</v>
+        <v>-88000</v>
       </c>
       <c r="S10" t="n">
-        <v>30000</v>
+        <v>6000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>영업이익 223% 증가 등 호실적 발표. AI 최종 수혜주 가능성 언급. 도배글 및 투자 주의 언급.</t>
+          <t>대한광통신, 유리기판 특허 관련 기대감. 미국 전력 및 통신/반도체 업황 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업이익', 'AI 수혜주', '실적발표']</t>
+          <t>['유리기판', '특허', '업황']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16520</v>
+        <v>16510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.35%</t>
+          <t>'+1.29%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H11" t="n">
         <v>27.96</v>
@@ -1438,7 +1438,7 @@
         <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>33620552860</v>
+        <v>34493425760</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14750</v>
+        <v>14870</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'+1.23%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.46</v>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G12" t="n">
-        <v>517</v>
+        <v>539</v>
       </c>
       <c r="H12" t="n">
         <v>7.82</v>
@@ -1530,7 +1530,7 @@
         <v>7.36</v>
       </c>
       <c r="O12" t="n">
-        <v>74197422425</v>
+        <v>75763519050</v>
       </c>
       <c r="P12" t="n">
         <v>49800</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>연기금의 꾸준한 매수세와 함께 루닛스코프, AI 신약 개발 활용 등 성장성 및 확장성에 대한 긍정적 전망이 제시됨. 공매도 숏커버링 기대감과 AZ 3상 결과 등 추가적인 레벨업 가능성이 언급됨.</t>
+          <t>의료 AI 대장주로서 견고한 성장성 및 확장성 보유. 해외 수출 및 신약 개발 활용 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI 신약 개발', '성장성', '공매도 숏커버링']</t>
+          <t>['의료AI', '성장성', '신약개발']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26600</v>
+        <v>26500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.38%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="H13" t="n">
         <v>12.32</v>
@@ -1622,7 +1622,7 @@
         <v>12.39</v>
       </c>
       <c r="O13" t="n">
-        <v>39474908175</v>
+        <v>40123573325</v>
       </c>
       <c r="P13" t="n">
         <v>59300</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34550</v>
+        <v>34900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.34%</t>
+          <t>'-4.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G14" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1714,7 +1714,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>101815870375</v>
+        <v>104187435125</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>

--- a/data/trending_integrated_20261027_13.xlsx
+++ b/data/trending_integrated_20261027_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41939402760</v>
+        <v>41942774550</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18727819665</v>
+        <v>18728144375</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 소식과 함께 나무가가 LG이노텍을 제치고 주요 부품을 공급한다는 점이 부각됨. 3D 센싱 카메라 독점 공급 및 텐버거 기대감이 제시되며, 3분기 실적 어닝 서프라이즈 가능성도 언급됨.</t>
+          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 및 3D 센싱 카메라 독점 공급 호재. 텐버거 기대감 형성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['휴머노이드 로봇', '3D 센싱 카메라', '실적 어닝 서프라이즈']</t>
+          <t>['휴머노이드', '로봇', '3D센싱']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20500</v>
+        <v>20650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.61%</t>
+          <t>'+8.40%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H4" t="n">
         <v>0.3</v>
@@ -794,7 +794,7 @@
         <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>67596430090</v>
+        <v>67831214540</v>
       </c>
       <c r="P4" t="n">
         <v>62100</v>
@@ -803,23 +803,23 @@
         <v>14600</v>
       </c>
       <c r="R4" t="n">
-        <v>7000</v>
+        <v>24000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 기업으로 분류. 기술적 분석상 양음 라인 형성 및 단기 급등 가능성 언급.</t>
+          <t>로봇 테마 기대감과 함께 상승 여력 언급. 단기 급등 및 피뢰침 현상 관찰.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', '기술적분석', '흑자기업']</t>
+          <t>['로봇', '테마주', '단타']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1358000</v>
+        <v>1356000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.51%</t>
+          <t>'+6.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G5" t="n">
-        <v>1607</v>
+        <v>1625</v>
       </c>
       <c r="H5" t="n">
         <v>48.66</v>
@@ -886,7 +886,7 @@
         <v>48.69</v>
       </c>
       <c r="O5" t="n">
-        <v>2559757294500</v>
+        <v>2596098623500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -895,23 +895,23 @@
         <v>501000</v>
       </c>
       <c r="R5" t="n">
-        <v>174000</v>
+        <v>53000</v>
       </c>
       <c r="S5" t="n">
-        <v>50000</v>
+        <v>166000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>실적 발표 이후 주가 상승 기대. 외국인, 기관 쌍끌이 매수세 유입.</t>
+          <t>실적 발표 전후로 긍정적 전망과 함께 변동성 예상. 외국인, 기관 매수세 관찰.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적발표', '외국인기관', '주주환원']</t>
+          <t>['실적발표', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>-0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H6" t="n">
         <v>4.89</v>
@@ -978,7 +978,7 @@
         <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>45348572023</v>
+        <v>46751179923</v>
       </c>
       <c r="P6" t="n">
         <v>4980</v>
@@ -987,23 +987,23 @@
         <v>749</v>
       </c>
       <c r="R6" t="n">
-        <v>-89000</v>
+        <v>-41000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>로봇 관련주로 분류. 변동성 속 종가 관리 움직임.</t>
+          <t>로봇 관련 기대감 속 상승세 전망. 투자주의 종목 지정 및 변동성 유의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['로봇', '변동성', '종가관리']</t>
+          <t>['로봇', '스마트팩토리', '자동화']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G7" t="n">
-        <v>1283</v>
+        <v>1332</v>
       </c>
       <c r="H7" t="n">
         <v>46.1</v>
@@ -1070,7 +1070,7 @@
         <v>46.11</v>
       </c>
       <c r="O7" t="n">
-        <v>1838068831000</v>
+        <v>1887232219750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1079,23 +1079,23 @@
         <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>1019000</v>
+        <v>1190000</v>
       </c>
       <c r="S7" t="n">
-        <v>432000</v>
+        <v>624000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>실적 및 주주환원 발표 기대감 속 외인 매도세 지속. 대외 변수 영향.</t>
+          <t>실적 및 주주환원 발표 기대감 속 혼조세. 외인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주주환원', '외인매도', '실적발표']</t>
+          <t>['주주환원', '실적', '외인']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62200</v>
+        <v>62400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.01%</t>
+          <t>'+4.35%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F8" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G8" t="n">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="H8" t="n">
         <v>40.44</v>
@@ -1162,7 +1162,7 @@
         <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>213265368450</v>
+        <v>216000661350</v>
       </c>
       <c r="P8" t="n">
         <v>67300</v>
@@ -1171,10 +1171,10 @@
         <v>23150</v>
       </c>
       <c r="R8" t="n">
-        <v>195000</v>
+        <v>219000</v>
       </c>
       <c r="S8" t="n">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1207,184 +1207,184 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14650</v>
+        <v>13750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.02%</t>
+          <t>'+2.77%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>367</v>
+        <v>297</v>
       </c>
       <c r="H9" t="n">
-        <v>10.02</v>
+        <v>2.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14220</v>
+        <v>13380</v>
       </c>
       <c r="K9" t="n">
-        <v>14390</v>
+        <v>14000</v>
       </c>
       <c r="L9" t="n">
-        <v>15150</v>
+        <v>14410</v>
       </c>
       <c r="M9" t="n">
-        <v>14390</v>
+        <v>13660</v>
       </c>
       <c r="N9" t="n">
-        <v>10.03</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>35501269150</v>
+        <v>56622498560</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>1760</v>
       </c>
       <c r="R9" t="n">
-        <v>392000</v>
+        <v>-212000</v>
       </c>
       <c r="S9" t="n">
-        <v>30000</v>
+        <v>6000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>영업이익 223% 증가 등 견조한 실적 발표. AI 수혜 기대감.</t>
+          <t>대한광통신, 유리기판 특허 관련 기대감. 미국 전력 및 통신/반도체 업황 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['영업이익', '실적발표', 'AI수혜']</t>
+          <t>['유리기판', '특허', '업황']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13740</v>
+        <v>14570</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.69%</t>
+          <t>'+2.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
-        <v>298</v>
+        <v>384</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>10.02</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13380</v>
+        <v>14220</v>
       </c>
       <c r="K10" t="n">
-        <v>14000</v>
+        <v>14390</v>
       </c>
       <c r="L10" t="n">
-        <v>14410</v>
+        <v>15150</v>
       </c>
       <c r="M10" t="n">
-        <v>13660</v>
+        <v>14390</v>
       </c>
       <c r="N10" t="n">
-        <v>2.82</v>
+        <v>10.03</v>
       </c>
       <c r="O10" t="n">
-        <v>56298579930</v>
+        <v>36202499365</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>1760</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-88000</v>
+        <v>197000</v>
       </c>
       <c r="S10" t="n">
-        <v>6000</v>
+        <v>38000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대한광통신, 유리기판 특허 관련 기대감. 미국 전력 및 통신/반도체 업황 언급.</t>
+          <t>223% 영업이익 증가 실적 발표에 대한 긍정적 반응. 도배성 글 경계.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유리기판', '특허', '업황']</t>
+          <t>['영업이익', '실적발표', '도배']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16510</v>
+        <v>16480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.29%</t>
+          <t>'+1.10%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
         <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="H11" t="n">
         <v>27.96</v>
@@ -1438,7 +1438,7 @@
         <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>34493425760</v>
+        <v>35698043160</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1447,10 +1447,10 @@
         <v>16290</v>
       </c>
       <c r="R11" t="n">
-        <v>118000</v>
+        <v>125000</v>
       </c>
       <c r="S11" t="n">
-        <v>1000</v>
+        <v>-32000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14870</v>
+        <v>14720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.23%</t>
+          <t>'+0.20%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.46</v>
       </c>
       <c r="E12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G12" t="n">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="H12" t="n">
         <v>7.82</v>
@@ -1530,7 +1530,7 @@
         <v>7.36</v>
       </c>
       <c r="O12" t="n">
-        <v>75763519050</v>
+        <v>76830960905</v>
       </c>
       <c r="P12" t="n">
         <v>49800</v>
@@ -1539,10 +1539,10 @@
         <v>8180</v>
       </c>
       <c r="R12" t="n">
-        <v>264000</v>
+        <v>50000</v>
       </c>
       <c r="S12" t="n">
-        <v>67000</v>
+        <v>109000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26500</v>
+        <v>26450</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.19%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H13" t="n">
         <v>12.32</v>
@@ -1622,7 +1622,7 @@
         <v>12.39</v>
       </c>
       <c r="O13" t="n">
-        <v>40123573325</v>
+        <v>40817853725</v>
       </c>
       <c r="P13" t="n">
         <v>59300</v>
@@ -1631,23 +1631,23 @@
         <v>22000</v>
       </c>
       <c r="R13" t="n">
-        <v>-225000</v>
+        <v>-236000</v>
       </c>
       <c r="S13" t="n">
-        <v>-32000</v>
+        <v>-68000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3분기 실적 예상치 하향 및 부정적 전망. 개인 매수세만 관찰됨.</t>
+          <t>3분기 실적에 대한 우려와 함께 부정적 전망 우세. 주가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적', 'AMPC', '개인매수']</t>
+          <t>['실적', '주가', '전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34900</v>
+        <v>34650</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.38%</t>
+          <t>'-5.07%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F14" t="n">
         <v>92</v>
       </c>
       <c r="G14" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1714,7 +1714,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>104187435125</v>
+        <v>105743638725</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>
@@ -1723,14 +1723,14 @@
         <v>15260</v>
       </c>
       <c r="R14" t="n">
-        <v>-131000</v>
+        <v>-393000</v>
       </c>
       <c r="S14" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>전년비 157% 영업이익 상승에도 불구하고 주가 하락. 외인 매도 및 프로그램 매수세 부재. 컨센서스 미달 및 하한가 우려.</t>
+          <t>실적 개선에도 불구하고 주가 하락 및 하한가 가능성 제기. 프로그램 매도세 관찰.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '외인', '하한가']</t>
+          <t>['실적', '하한가', '외인']</t>
         </is>
       </c>
       <c r="X14" t="n">

--- a/data/trending_integrated_20261027_13.xlsx
+++ b/data/trending_integrated_20261027_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41942774550</v>
+        <v>41952130080</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18728144375</v>
+        <v>18735698155</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20650</v>
+        <v>20550</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.40%</t>
+          <t>'+7.87%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H4" t="n">
         <v>0.3</v>
@@ -794,7 +794,7 @@
         <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>67831214540</v>
+        <v>68222390390</v>
       </c>
       <c r="P4" t="n">
         <v>62100</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 테마 기대감과 함께 상승 여력 언급. 단기 급등 및 피뢰침 현상 관찰.</t>
+          <t>로봇 관련주로 분류되며 흑자 기업. 테슬라 폭등에 따른 기대감 및 상승 여력 언급. 단기 급등 후 차익 실현 및 보호예수 물량 부담 가능성 존재. 기술적 분석 기반 단타 매매 동향.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', '테마주', '단타']</t>
+          <t>['로봇', '흑자 기업', '단기 급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1356000</v>
+        <v>2180</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.35%</t>
+          <t>'+7.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>104</v>
       </c>
       <c r="F5" t="n">
-        <v>447</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>1625</v>
+        <v>176</v>
       </c>
       <c r="H5" t="n">
-        <v>48.66</v>
+        <v>4.89</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1275000</v>
+        <v>2035</v>
       </c>
       <c r="K5" t="n">
-        <v>1346000</v>
+        <v>2035</v>
       </c>
       <c r="L5" t="n">
-        <v>1381000</v>
+        <v>2300</v>
       </c>
       <c r="M5" t="n">
-        <v>1341000</v>
+        <v>1953</v>
       </c>
       <c r="N5" t="n">
-        <v>48.69</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>2596098623500</v>
+        <v>48053922391</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>4980</v>
       </c>
       <c r="Q5" t="n">
-        <v>501000</v>
+        <v>749</v>
       </c>
       <c r="R5" t="n">
-        <v>53000</v>
+        <v>-41000</v>
       </c>
       <c r="S5" t="n">
-        <v>166000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>실적 발표 전후로 긍정적 전망과 함께 변동성 예상. 외국인, 기관 매수세 관찰.</t>
+          <t>로봇 및 스마트팩토리 관련주로 분류. 변동성 장세 속 개미 털기 및 상장 기대감 혼재. 단기 급등 후 차익 실현 가능성 및 파동 분석 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적발표', '외국인', '기관']</t>
+          <t>['로봇', '스마트팩토리', '변동성']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2160</v>
+        <v>1357000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.14%</t>
+          <t>'+6.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.11</v>
+        <v>-0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>447</v>
       </c>
       <c r="G6" t="n">
-        <v>170</v>
+        <v>1670</v>
       </c>
       <c r="H6" t="n">
-        <v>4.89</v>
+        <v>48.66</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2035</v>
+        <v>1275000</v>
       </c>
       <c r="K6" t="n">
-        <v>2035</v>
+        <v>1346000</v>
       </c>
       <c r="L6" t="n">
-        <v>2300</v>
+        <v>1381000</v>
       </c>
       <c r="M6" t="n">
-        <v>1953</v>
+        <v>1341000</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>46751179923</v>
+        <v>2628596047000</v>
       </c>
       <c r="P6" t="n">
-        <v>4980</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>749</v>
+        <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>-41000</v>
+        <v>53000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>166000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>로봇 관련 기대감 속 상승세 전망. 투자주의 종목 지정 및 변동성 유의.</t>
+          <t>실적 발표 후 랠리 및 150만원 돌파 기대감 존재. 외국인/기관 동시 매수세 유입 및 주주환원 발표 가능성 언급. 엔트로픽 상장 관련 HBM 이슈 주목. 공포 조정 구간 통과 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['로봇', '스마트팩토리', '자동화']</t>
+          <t>['실적 발표', '외국인/기관 동시 매수', 'HBM']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>222750</v>
+        <v>222500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.58%</t>
+          <t>'+4.46%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="G7" t="n">
-        <v>1332</v>
+        <v>1325</v>
       </c>
       <c r="H7" t="n">
         <v>46.1</v>
@@ -1070,7 +1070,7 @@
         <v>46.11</v>
       </c>
       <c r="O7" t="n">
-        <v>1887232219750</v>
+        <v>1929481855500</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>실적 및 주주환원 발표 기대감 속 혼조세. 외인 매도세 관찰.</t>
+          <t>실적 발표 및 주주환원 기대감 속 외인 매도세 지속. SK하이닉스 ETF 편출, HBM 부족 이슈로 인한 기술주 투자 심리 위축. 30만원 재진입 및 급등 기대감과 하락 전망 혼재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주주환원', '실적', '외인']</t>
+          <t>['실적 발표', '주주환원', '외인 매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F8" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G8" t="n">
-        <v>855</v>
+        <v>864</v>
       </c>
       <c r="H8" t="n">
         <v>40.44</v>
@@ -1162,7 +1162,7 @@
         <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>216000661350</v>
+        <v>219656834150</v>
       </c>
       <c r="P8" t="n">
         <v>67300</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13750</v>
+        <v>13720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.77%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="H9" t="n">
         <v>2.82</v>
@@ -1254,7 +1254,7 @@
         <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>56622498560</v>
+        <v>56927052140</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14570</v>
+        <v>14535</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.46%</t>
+          <t>'+2.22%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F10" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="H10" t="n">
         <v>10.02</v>
@@ -1346,7 +1346,7 @@
         <v>10.03</v>
       </c>
       <c r="O10" t="n">
-        <v>36202499365</v>
+        <v>36729217635</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>223% 영업이익 증가 실적 발표에 대한 긍정적 반응. 도배성 글 경계.</t>
+          <t>영업이익 223% 증가 호재에도 불구, 반등 없는 주가 흐름. 도배성 글 다수 게시 및 투자자 간 의견 대립. AI 수혜주 전망 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업이익', '실적발표', '도배']</t>
+          <t>['영업이익', '실적 발표', 'AI 수혜주']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16480</v>
+        <v>16360</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.10%</t>
+          <t>'+0.37%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F11" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="H11" t="n">
         <v>27.96</v>
@@ -1432,13 +1432,13 @@
         <v>16770</v>
       </c>
       <c r="M11" t="n">
-        <v>16410</v>
+        <v>16350</v>
       </c>
       <c r="N11" t="n">
         <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>35698043160</v>
+        <v>37476678260</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14720</v>
+        <v>14700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.20%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>155</v>
       </c>
       <c r="F12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G12" t="n">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="H12" t="n">
         <v>7.82</v>
@@ -1530,7 +1530,7 @@
         <v>7.36</v>
       </c>
       <c r="O12" t="n">
-        <v>76830960905</v>
+        <v>77578913835</v>
       </c>
       <c r="P12" t="n">
         <v>49800</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>의료 AI 대장주로서 견고한 성장성 및 확장성 보유. 해외 수출 및 신약 개발 활용 기대.</t>
+          <t>해외 수출 확대, 신약 개발 활용 등 성장성 및 확장성 기반 긍정적 전망. 루닛스코프, scope insight 등 기술력 언급. 공매도 숏커버링 및 해외 인수합병 가능성 제기. AZ 3상 결과 주목.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['의료AI', '성장성', '신약개발']</t>
+          <t>['해외 수출', '신약 개발', '성장성']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="H13" t="n">
         <v>12.32</v>
@@ -1622,7 +1622,7 @@
         <v>12.39</v>
       </c>
       <c r="O13" t="n">
-        <v>40817853725</v>
+        <v>41945798200</v>
       </c>
       <c r="P13" t="n">
         <v>59300</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3분기 실적에 대한 우려와 함께 부정적 전망 우세. 주가 하락 가능성 언급.</t>
+          <t>3분기 실적 악화 우려 및 유증 관련 부정적 전망. 태양광 업황 부진 및 환율 영향 언급. JP모건 목표주가 하향 조정 루머 존재. 반도체 관련 기대감 일부 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적', '주가', '전망']</t>
+          <t>['3분기 실적', '유증', '태양광']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34650</v>
+        <v>34700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.07%</t>
+          <t>'-4.93%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F14" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G14" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1714,7 +1714,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>105743638725</v>
+        <v>107111113300</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 개선에도 불구하고 주가 하락 및 하한가 가능성 제기. 프로그램 매도세 관찰.</t>
+          <t>실적 호조에도 불구하고 급락 및 하한가 기록. 외인 매도세 지속 및 프로그램 매매 동향 주목. 주가 하락 이유에 대한 불확실성 및 정부 정책 비판. 엔트로픽 관련주 영향 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적', '하한가', '외인']</t>
+          <t>['실적 호조', '급락', '외인 매도']</t>
         </is>
       </c>
       <c r="X14" t="n">

--- a/data/trending_integrated_20261027_13.xlsx
+++ b/data/trending_integrated_20261027_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41952130080</v>
+        <v>41955596850</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18735698155</v>
+        <v>18736057045</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 및 3D 센싱 카메라 독점 공급 호재. 텐버거 기대감 형성.</t>
+          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 소식과 함께 나무가가 LG이노텍을 제치고 주요 부품을 공급한다는 점이 부각됨. 3D 센싱 카메라 독점 공급 및 텐버거 기대감이 제시되며, 3분기 실적 어닝 서프라이즈 가능성도 언급됨.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['휴머노이드', '로봇', '3D센싱']</t>
+          <t>['휴머노이드 로봇', '3D 센싱 카메라', '실적 어닝 서프라이즈']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20550</v>
+        <v>2170</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.87%</t>
+          <t>'+6.63%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3</v>
+        <v>4.89</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19050</v>
+        <v>2035</v>
       </c>
       <c r="K4" t="n">
-        <v>19450</v>
+        <v>2035</v>
       </c>
       <c r="L4" t="n">
-        <v>22450</v>
+        <v>2300</v>
       </c>
       <c r="M4" t="n">
-        <v>18430</v>
+        <v>1953</v>
       </c>
       <c r="N4" t="n">
-        <v>0.18</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>68222390390</v>
+        <v>48502469830</v>
       </c>
       <c r="P4" t="n">
-        <v>62100</v>
+        <v>4980</v>
       </c>
       <c r="Q4" t="n">
-        <v>14600</v>
+        <v>749</v>
       </c>
       <c r="R4" t="n">
-        <v>24000</v>
+        <v>-41000</v>
       </c>
       <c r="S4" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 관련주로 분류되며 흑자 기업. 테슬라 폭등에 따른 기대감 및 상승 여력 언급. 단기 급등 후 차익 실현 및 보호예수 물량 부담 가능성 존재. 기술적 분석 기반 단타 매매 동향.</t>
+          <t>로봇 관련주로서의 상승 기대감 및 긍정적 흐름 언급. 투자 주의 예고 및 일부 변동성 수반에 대한 우려 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', '흑자 기업', '단기 급등']</t>
+          <t>['로봇', '상승 기대감', '변동성']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2180</v>
+        <v>20150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.13%</t>
+          <t>'+5.77%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="H5" t="n">
-        <v>4.89</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2035</v>
+        <v>19050</v>
       </c>
       <c r="K5" t="n">
-        <v>2035</v>
+        <v>19450</v>
       </c>
       <c r="L5" t="n">
-        <v>2300</v>
+        <v>22450</v>
       </c>
       <c r="M5" t="n">
-        <v>1953</v>
+        <v>18430</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>48053922391</v>
+        <v>68818069690</v>
       </c>
       <c r="P5" t="n">
-        <v>4980</v>
+        <v>62100</v>
       </c>
       <c r="Q5" t="n">
-        <v>749</v>
+        <v>14600</v>
       </c>
       <c r="R5" t="n">
-        <v>-41000</v>
+        <v>24000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇 및 스마트팩토리 관련주로 분류. 변동성 장세 속 개미 털기 및 상장 기대감 혼재. 단기 급등 후 차익 실현 가능성 및 파동 분석 언급.</t>
+          <t>로봇 기업으로서의 잠재력 언급에도 불구하고 뚜렷한 상승 모멘텀 부족. 단기 급등락 및 기술적 분석에 대한 의견 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇', '스마트팩토리', '변동성']</t>
+          <t>['로봇', '상승 여력', '단타']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1357000</v>
+        <v>1345000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.43%</t>
+          <t>'+5.49%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G6" t="n">
-        <v>1670</v>
+        <v>1659</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>2628596047000</v>
+        <v>2674739030500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>실적 발표 후 랠리 및 150만원 돌파 기대감 존재. 외국인/기관 동시 매수세 유입 및 주주환원 발표 가능성 언급. 엔트로픽 상장 관련 HBM 이슈 주목. 공포 조정 구간 통과 전망.</t>
+          <t>실적 발표 및 주주환원 기대감 속 외국인, 기관 동시 매수세 유입. 단기 급등 후 조정 구간에 대한 의견 분분.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적 발표', '외국인/기관 동시 매수', 'HBM']</t>
+          <t>['실적 발표', '주주환원', '외국인 기관']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>222500</v>
+        <v>221250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.46%</t>
+          <t>'+3.87%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="G7" t="n">
-        <v>1325</v>
+        <v>1315</v>
       </c>
       <c r="H7" t="n">
         <v>46.1</v>
@@ -1070,7 +1070,7 @@
         <v>46.11</v>
       </c>
       <c r="O7" t="n">
-        <v>1929481855500</v>
+        <v>1987308848000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>실적 발표 및 주주환원 기대감 속 외인 매도세 지속. SK하이닉스 ETF 편출, HBM 부족 이슈로 인한 기술주 투자 심리 위축. 30만원 재진입 및 급등 기대감과 하락 전망 혼재.</t>
+          <t>실적 및 주주환원 발표 기대감 속 공매도 세력 청산 가능성 언급. 다만, 외인 매도세 및 부정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['실적 발표', '주주환원', '외인 매도']</t>
+          <t>['주주환원', '공매도', '실적']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62400</v>
+        <v>62100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.35%</t>
+          <t>'+3.85%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F8" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G8" t="n">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="H8" t="n">
         <v>40.44</v>
@@ -1162,7 +1162,7 @@
         <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>219656834150</v>
+        <v>222966647350</v>
       </c>
       <c r="P8" t="n">
         <v>67300</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13720</v>
+        <v>13660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.09%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="H9" t="n">
         <v>2.82</v>
@@ -1248,13 +1248,13 @@
         <v>14410</v>
       </c>
       <c r="M9" t="n">
-        <v>13660</v>
+        <v>13640</v>
       </c>
       <c r="N9" t="n">
         <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>56927052140</v>
+        <v>57893276415</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대한광통신, 유리기판 특허 관련 기대감. 미국 전력 및 통신/반도체 업황 언급.</t>
+          <t>미국 빅테크 AI 데이터센터향 핵심 규격 통과 및 GR-20 인증 획득. 긍정적 호재 연달아 발생하며 상승 전망 우세. 공매도 세력 애먹는다는 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유리기판', '특허', '업황']</t>
+          <t>['AI 데이터센터', '광케이블', 'GR-20 인증']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14535</v>
+        <v>14480</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.22%</t>
+          <t>'+1.83%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F10" t="n">
         <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="H10" t="n">
         <v>10.02</v>
@@ -1346,7 +1346,7 @@
         <v>10.03</v>
       </c>
       <c r="O10" t="n">
-        <v>36729217635</v>
+        <v>37694840965</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>영업이익 223% 증가 호재에도 불구, 반등 없는 주가 흐름. 도배성 글 다수 게시 및 투자자 간 의견 대립. AI 수혜주 전망 존재.</t>
+          <t>영업이익 223% 증가라는 긍정적 실적 발표에도 불구하고 반등 없는 주가에 대한 실망감. 도배글 및 일부 부정적 의견 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업이익', '실적 발표', 'AI 수혜주']</t>
+          <t>['영업이익', '실적 발표', '반등']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16360</v>
+        <v>16450</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.37%</t>
+          <t>'+0.92%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="H11" t="n">
         <v>27.96</v>
@@ -1432,19 +1432,19 @@
         <v>16770</v>
       </c>
       <c r="M11" t="n">
-        <v>16350</v>
+        <v>16270</v>
       </c>
       <c r="N11" t="n">
         <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>37476678260</v>
+        <v>39543454870</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>16290</v>
+        <v>16270</v>
       </c>
       <c r="R11" t="n">
         <v>125000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼성중공업, 주가 조작 및 공매도 관련 불만 표출. 조선주 하락세 언급.</t>
+          <t>외국인 및 기관 매수세 언급에도 불구하고 주가 부진 및 부정적 전망이 우세. 저가 인식 및 비관적 견해 다수.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '조선주']</t>
+          <t>['외국인 매수', '주가 부진', '부정적 전망']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1483,79 +1483,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14700</v>
+        <v>26400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'-0.38%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.46</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>557</v>
+        <v>275</v>
       </c>
       <c r="H12" t="n">
-        <v>7.82</v>
+        <v>12.32</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14690</v>
+        <v>26500</v>
       </c>
       <c r="K12" t="n">
-        <v>14490</v>
+        <v>26600</v>
       </c>
       <c r="L12" t="n">
-        <v>15800</v>
+        <v>27200</v>
       </c>
       <c r="M12" t="n">
-        <v>14260</v>
+        <v>25350</v>
       </c>
       <c r="N12" t="n">
-        <v>7.36</v>
+        <v>12.39</v>
       </c>
       <c r="O12" t="n">
-        <v>77578913835</v>
+        <v>44317614150</v>
       </c>
       <c r="P12" t="n">
-        <v>49800</v>
+        <v>59300</v>
       </c>
       <c r="Q12" t="n">
-        <v>8180</v>
+        <v>22000</v>
       </c>
       <c r="R12" t="n">
-        <v>50000</v>
+        <v>-236000</v>
       </c>
       <c r="S12" t="n">
-        <v>109000</v>
+        <v>-68000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>해외 수출 확대, 신약 개발 활용 등 성장성 및 확장성 기반 긍정적 전망. 루닛스코프, scope insight 등 기술력 언급. 공매도 숏커버링 및 해외 인수합병 가능성 제기. AZ 3상 결과 주목.</t>
+          <t>3분기 실적 악화 우려 및 유증 관련 부정적 전망. 태양광 업황 부진 및 환율 영향 언급. JP모건 목표주가 하향 조정 루머 존재. 반도체 관련 기대감 일부 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['해외 수출', '신약 개발', '성장성']</t>
+          <t>['3분기 실적', '유증', '태양광']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,86 +1568,86 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26450</v>
+        <v>14520</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.19%</t>
+          <t>'-1.16%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="G13" t="n">
-        <v>272</v>
+        <v>558</v>
       </c>
       <c r="H13" t="n">
-        <v>12.32</v>
+        <v>7.82</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>26500</v>
+        <v>14690</v>
       </c>
       <c r="K13" t="n">
-        <v>26600</v>
+        <v>14490</v>
       </c>
       <c r="L13" t="n">
-        <v>27200</v>
+        <v>15800</v>
       </c>
       <c r="M13" t="n">
-        <v>25350</v>
+        <v>14260</v>
       </c>
       <c r="N13" t="n">
-        <v>12.39</v>
+        <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>41945798200</v>
+        <v>78344959165</v>
       </c>
       <c r="P13" t="n">
-        <v>59300</v>
+        <v>49800</v>
       </c>
       <c r="Q13" t="n">
-        <v>22000</v>
+        <v>8180</v>
       </c>
       <c r="R13" t="n">
-        <v>-236000</v>
+        <v>50000</v>
       </c>
       <c r="S13" t="n">
-        <v>-68000</v>
+        <v>109000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3분기 실적 악화 우려 및 유증 관련 부정적 전망. 태양광 업황 부진 및 환율 영향 언급. JP모건 목표주가 하향 조정 루머 존재. 반도체 관련 기대감 일부 존재.</t>
+          <t>의료 AI 분야에서의 확장성 및 성장성에 대한 긍정적 전망. 해외 수출 및 신약 개발 활용 등 구체적 언급 다수. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['3분기 실적', '유증', '태양광']</t>
+          <t>['의료 AI', '성장성', '해외 수출']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34700</v>
+        <v>34550</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.93%</t>
+          <t>'-5.34%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G14" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1714,7 +1714,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>107111113300</v>
+        <v>107948546275</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 호조에도 불구하고 급락 및 하한가 기록. 외인 매도세 지속 및 프로그램 매매 동향 주목. 주가 하락 이유에 대한 불확실성 및 정부 정책 비판. 엔트로픽 관련주 영향 언급.</t>
+          <t>실적 호조에도 불구하고 주가 하락 및 부정적 전망이 지배적. 외인 매도세 및 급락 가능성에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적 호조', '급락', '외인 매도']</t>
+          <t>['실적', '주가 하락', '외인 매도']</t>
         </is>
       </c>
       <c r="X14" t="n">

--- a/data/trending_integrated_20261027_13.xlsx
+++ b/data/trending_integrated_20261027_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
         <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41955596850</v>
+        <v>41960345850</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18736057045</v>
+        <v>18736330485</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 소식과 함께 나무가가 LG이노텍을 제치고 주요 부품을 공급한다는 점이 부각됨. 3D 센싱 카메라 독점 공급 및 텐버거 기대감이 제시되며, 3분기 실적 어닝 서프라이즈 가능성도 언급됨.</t>
+          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 및 3D 센싱 카메라 독점 공급 기대감. 삼성 비스포크 AI 로봇청소기 납품 가능성 언급. 텐버거 가능성 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['휴머노이드 로봇', '3D 센싱 카메라', '실적 어닝 서프라이즈']</t>
+          <t>['휴머노이드 로봇', '3D 센싱 카메라', '아틀라스']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2170</v>
+        <v>8930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.63%</t>
+          <t>'+25.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>200</v>
+        <v>139</v>
       </c>
       <c r="H4" t="n">
-        <v>4.89</v>
+        <v>2.12</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2035</v>
+        <v>7100</v>
       </c>
       <c r="K4" t="n">
-        <v>2035</v>
+        <v>7170</v>
       </c>
       <c r="L4" t="n">
-        <v>2300</v>
+        <v>9190</v>
       </c>
       <c r="M4" t="n">
-        <v>1953</v>
+        <v>7160</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>48502469830</v>
+        <v>43299566515</v>
       </c>
       <c r="P4" t="n">
-        <v>4980</v>
+        <v>29750</v>
       </c>
       <c r="Q4" t="n">
-        <v>749</v>
+        <v>6570</v>
       </c>
       <c r="R4" t="n">
-        <v>-41000</v>
+        <v>59000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 관련주로서의 상승 기대감 및 긍정적 흐름 언급. 투자 주의 예고 및 일부 변동성 수반에 대한 우려 존재.</t>
+          <t>엔트로픽 상장 최대 수혜주로 언급되며 어닝 서프라이즈 및 급등 기대감. 차트상 추가 상승 여력 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', '상승 기대감', '변동성']</t>
+          <t>['엔트로픽', '어닝 서프라이즈', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20150</v>
+        <v>2170</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.77%</t>
+          <t>'+6.63%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>4.89</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>19050</v>
+        <v>2035</v>
       </c>
       <c r="K5" t="n">
-        <v>19450</v>
+        <v>2035</v>
       </c>
       <c r="L5" t="n">
-        <v>22450</v>
+        <v>2300</v>
       </c>
       <c r="M5" t="n">
-        <v>18430</v>
+        <v>1953</v>
       </c>
       <c r="N5" t="n">
-        <v>0.18</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>68818069690</v>
+        <v>49019682669</v>
       </c>
       <c r="P5" t="n">
-        <v>62100</v>
+        <v>4980</v>
       </c>
       <c r="Q5" t="n">
-        <v>14600</v>
+        <v>749</v>
       </c>
       <c r="R5" t="n">
-        <v>24000</v>
+        <v>-41000</v>
       </c>
       <c r="S5" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇 기업으로서의 잠재력 언급에도 불구하고 뚜렷한 상승 모멘텀 부족. 단기 급등락 및 기술적 분석에 대한 의견 존재.</t>
+          <t>로봇 관련주로서 스마트 팩토리 및 자동화 테마 언급. 흑자 전환 기대감 속 변동성 장세.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇', '상승 여력', '단타']</t>
+          <t>['로봇', '스마트 팩토리', '변동성']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1345000</v>
+        <v>20300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.49%</t>
+          <t>'+6.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>446</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>1659</v>
+        <v>157</v>
       </c>
       <c r="H6" t="n">
-        <v>48.66</v>
+        <v>0.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1275000</v>
+        <v>19050</v>
       </c>
       <c r="K6" t="n">
-        <v>1346000</v>
+        <v>19450</v>
       </c>
       <c r="L6" t="n">
-        <v>1381000</v>
+        <v>22450</v>
       </c>
       <c r="M6" t="n">
-        <v>1341000</v>
+        <v>18430</v>
       </c>
       <c r="N6" t="n">
-        <v>48.69</v>
+        <v>0.18</v>
       </c>
       <c r="O6" t="n">
-        <v>2674739030500</v>
+        <v>69200282240</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>62100</v>
       </c>
       <c r="Q6" t="n">
-        <v>501000</v>
+        <v>14600</v>
       </c>
       <c r="R6" t="n">
-        <v>53000</v>
+        <v>24000</v>
       </c>
       <c r="S6" t="n">
-        <v>166000</v>
+        <v>-1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>실적 발표 및 주주환원 기대감 속 외국인, 기관 동시 매수세 유입. 단기 급등 후 조정 구간에 대한 의견 분분.</t>
+          <t>로봇 기업으로 빅웨이브 및 흑자 기업임을 언급. 단기 변동성 및 기술적 분석 기반 상승 여력 논의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적 발표', '주주환원', '외국인 기관']</t>
+          <t>['로봇', '흑자기업', '기술적 분석']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>221250</v>
+        <v>1352000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.87%</t>
+          <t>'+6.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E7" t="n">
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G7" t="n">
-        <v>1315</v>
+        <v>1669</v>
       </c>
       <c r="H7" t="n">
-        <v>46.1</v>
+        <v>48.66</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>213000</v>
+        <v>1275000</v>
       </c>
       <c r="K7" t="n">
-        <v>222000</v>
+        <v>1346000</v>
       </c>
       <c r="L7" t="n">
-        <v>225500</v>
+        <v>1381000</v>
       </c>
       <c r="M7" t="n">
-        <v>221000</v>
+        <v>1341000</v>
       </c>
       <c r="N7" t="n">
-        <v>46.11</v>
+        <v>48.69</v>
       </c>
       <c r="O7" t="n">
-        <v>1987308848000</v>
+        <v>2710793796500</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>501000</v>
       </c>
       <c r="R7" t="n">
-        <v>1190000</v>
+        <v>53000</v>
       </c>
       <c r="S7" t="n">
-        <v>624000</v>
+        <v>166000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>실적 및 주주환원 발표 기대감 속 공매도 세력 청산 가능성 언급. 다만, 외인 매도세 및 부정적 전망 혼재.</t>
+          <t>실적 발표 후 반등 기대와 함께 외국인, 기관의 쌍끌이 매수세 관찰. 단기 조정 구간 탈피 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주주환원', '공매도', '실적']</t>
+          <t>['실적 발표', '기관', '외국인']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62100</v>
+        <v>222000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.85%</t>
+          <t>'+4.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>148</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>95</v>
+        <v>443</v>
       </c>
       <c r="G8" t="n">
-        <v>875</v>
+        <v>1318</v>
       </c>
       <c r="H8" t="n">
-        <v>40.44</v>
+        <v>46.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>59800</v>
+        <v>213000</v>
       </c>
       <c r="K8" t="n">
-        <v>60700</v>
+        <v>222000</v>
       </c>
       <c r="L8" t="n">
-        <v>63900</v>
+        <v>225500</v>
       </c>
       <c r="M8" t="n">
-        <v>60100</v>
+        <v>221000</v>
       </c>
       <c r="N8" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="O8" t="n">
-        <v>222966647350</v>
+        <v>2022149218000</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>219000</v>
+        <v>1190000</v>
       </c>
       <c r="S8" t="n">
-        <v>3000</v>
+        <v>624000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성그룹주 중 저평가 분석 및 MSCI 편입 기대감. 중동 전쟁 관련 불확실성 속 공매도 공세. 수주 공시 시 급등 전망.</t>
+          <t>실적 및 주주환원 발표 기대감과 함께 상승 전망. 공매도 세력의 대차 상환 움직임도 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['저평가', 'MSCI', '수주공시']</t>
+          <t>['실적', '주주환원', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13660</v>
+        <v>62100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.09%</t>
+          <t>'+3.85%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="G9" t="n">
-        <v>322</v>
+        <v>868</v>
       </c>
       <c r="H9" t="n">
-        <v>2.82</v>
+        <v>40.44</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13380</v>
+        <v>59800</v>
       </c>
       <c r="K9" t="n">
-        <v>14000</v>
+        <v>60700</v>
       </c>
       <c r="L9" t="n">
-        <v>14410</v>
+        <v>63900</v>
       </c>
       <c r="M9" t="n">
-        <v>13640</v>
+        <v>60100</v>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>40.39</v>
       </c>
       <c r="O9" t="n">
-        <v>57893276415</v>
+        <v>226242851050</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>67300</v>
       </c>
       <c r="Q9" t="n">
-        <v>1760</v>
+        <v>23150</v>
       </c>
       <c r="R9" t="n">
-        <v>-212000</v>
+        <v>219000</v>
       </c>
       <c r="S9" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 빅테크 AI 데이터센터향 핵심 규격 통과 및 GR-20 인증 획득. 긍정적 호재 연달아 발생하며 상승 전망 우세. 공매도 세력 애먹는다는 언급.</t>
+          <t>중동 관련 호재 및 그룹 내 저평가 인식. MSCI 편입 기대감과 대형 수주 공시 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광케이블', 'GR-20 인증']</t>
+          <t>['중동', ' MSCI', '수주']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,130 +1292,130 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14480</v>
+        <v>13710</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.83%</t>
+          <t>'+2.47%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>409</v>
+        <v>322</v>
       </c>
       <c r="H10" t="n">
-        <v>10.02</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14220</v>
+        <v>13380</v>
       </c>
       <c r="K10" t="n">
-        <v>14390</v>
+        <v>14000</v>
       </c>
       <c r="L10" t="n">
-        <v>15150</v>
+        <v>14410</v>
       </c>
       <c r="M10" t="n">
-        <v>14390</v>
+        <v>13610</v>
       </c>
       <c r="N10" t="n">
-        <v>10.03</v>
+        <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>37694840965</v>
+        <v>58421008060</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>1760</v>
       </c>
       <c r="R10" t="n">
-        <v>197000</v>
+        <v>-212000</v>
       </c>
       <c r="S10" t="n">
-        <v>38000</v>
+        <v>6000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>영업이익 223% 증가라는 긍정적 실적 발표에도 불구하고 반등 없는 주가에 대한 실망감. 도배글 및 일부 부정적 의견 존재.</t>
+          <t>미국 빅테크 AI 데이터센터향 핵심 규격 통과 및 GR-20 인증 획득. 긍정적 호재 연달아 발생하며 상승 전망 우세. 공매도 세력 애먹는다는 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업이익', '실적 발표', '반등']</t>
+          <t>['AI 데이터센터', '광케이블', 'GR-20 인증']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16450</v>
+        <v>14570</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.92%</t>
+          <t>'+2.46%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="F11" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>246</v>
+        <v>433</v>
       </c>
       <c r="H11" t="n">
-        <v>27.96</v>
+        <v>10.02</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16300</v>
+        <v>14220</v>
       </c>
       <c r="K11" t="n">
-        <v>16410</v>
+        <v>14390</v>
       </c>
       <c r="L11" t="n">
-        <v>16770</v>
+        <v>15150</v>
       </c>
       <c r="M11" t="n">
-        <v>16270</v>
+        <v>14390</v>
       </c>
       <c r="N11" t="n">
-        <v>27.94</v>
+        <v>10.03</v>
       </c>
       <c r="O11" t="n">
-        <v>39543454870</v>
+        <v>37995914275</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>16270</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>125000</v>
+        <v>197000</v>
       </c>
       <c r="S11" t="n">
-        <v>-32000</v>
+        <v>38000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 언급에도 불구하고 주가 부진 및 부정적 전망이 우세. 저가 인식 및 비관적 견해 다수.</t>
+          <t>영업이익 223% 증가 실적 발표에도 불구하고 주가 부진에 대한 우려. 도배성 글에 대한 비판.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['외국인 매수', '주가 부진', '부정적 전망']</t>
+          <t>['영업이익', '실적', '주가 부진']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26400</v>
+        <v>16540</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.38%</t>
+          <t>'+1.47%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>275</v>
+        <v>247</v>
       </c>
       <c r="H12" t="n">
-        <v>12.32</v>
+        <v>27.96</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>26500</v>
+        <v>16300</v>
       </c>
       <c r="K12" t="n">
-        <v>26600</v>
+        <v>16410</v>
       </c>
       <c r="L12" t="n">
-        <v>27200</v>
+        <v>16770</v>
       </c>
       <c r="M12" t="n">
-        <v>25350</v>
+        <v>16270</v>
       </c>
       <c r="N12" t="n">
-        <v>12.39</v>
+        <v>27.94</v>
       </c>
       <c r="O12" t="n">
-        <v>44317614150</v>
+        <v>40554544945</v>
       </c>
       <c r="P12" t="n">
-        <v>59300</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>22000</v>
+        <v>16270</v>
       </c>
       <c r="R12" t="n">
-        <v>-236000</v>
+        <v>125000</v>
       </c>
       <c r="S12" t="n">
-        <v>-68000</v>
+        <v>-32000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 실적 악화 우려 및 유증 관련 부정적 전망. 태양광 업황 부진 및 환율 영향 언급. JP모건 목표주가 하향 조정 루머 존재. 반도체 관련 기대감 일부 존재.</t>
+          <t>외국인 및 기관 매수세 언급에도 불구하고 주가 부진 및 부정적 전망이 우세. 저가 인식 및 비관적 견해 다수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['3분기 실적', '유증', '태양광']</t>
+          <t>['외국인 매수', '주가 부진', '부정적 전망']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,86 +1568,86 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14520</v>
+        <v>26450</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.16%</t>
+          <t>'-0.19%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.46</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="F13" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>558</v>
+        <v>286</v>
       </c>
       <c r="H13" t="n">
-        <v>7.82</v>
+        <v>12.32</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14690</v>
+        <v>26500</v>
       </c>
       <c r="K13" t="n">
-        <v>14490</v>
+        <v>26600</v>
       </c>
       <c r="L13" t="n">
-        <v>15800</v>
+        <v>27200</v>
       </c>
       <c r="M13" t="n">
-        <v>14260</v>
+        <v>25350</v>
       </c>
       <c r="N13" t="n">
-        <v>7.36</v>
+        <v>12.39</v>
       </c>
       <c r="O13" t="n">
-        <v>78344959165</v>
+        <v>44908982150</v>
       </c>
       <c r="P13" t="n">
-        <v>49800</v>
+        <v>59300</v>
       </c>
       <c r="Q13" t="n">
-        <v>8180</v>
+        <v>22000</v>
       </c>
       <c r="R13" t="n">
-        <v>50000</v>
+        <v>-236000</v>
       </c>
       <c r="S13" t="n">
-        <v>109000</v>
+        <v>-68000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>의료 AI 분야에서의 확장성 및 성장성에 대한 긍정적 전망. 해외 수출 및 신약 개발 활용 등 구체적 언급 다수. 공매도 숏커버링 가능성.</t>
+          <t>3분기 실적 발표에 대한 우려와 함께 주가 하락세 지속. 유증 관련 불만 및 태양광 업황 부진 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['의료 AI', '성장성', '해외 수출']</t>
+          <t>['실적', '주가 하락', '태양광']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34550</v>
+        <v>14560</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.34%</t>
+          <t>'-0.88%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.62</v>
+        <v>0.46</v>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G14" t="n">
-        <v>238</v>
+        <v>555</v>
       </c>
       <c r="H14" t="n">
-        <v>8.65</v>
+        <v>7.82</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,58 +1699,150 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>36500</v>
+        <v>14690</v>
       </c>
       <c r="K14" t="n">
-        <v>38750</v>
+        <v>14490</v>
       </c>
       <c r="L14" t="n">
-        <v>42150</v>
+        <v>15800</v>
       </c>
       <c r="M14" t="n">
-        <v>33550</v>
+        <v>14260</v>
       </c>
       <c r="N14" t="n">
-        <v>8.029999999999999</v>
+        <v>7.36</v>
       </c>
       <c r="O14" t="n">
-        <v>107948546275</v>
+        <v>79255986840</v>
       </c>
       <c r="P14" t="n">
-        <v>126600</v>
+        <v>49800</v>
       </c>
       <c r="Q14" t="n">
-        <v>15260</v>
+        <v>8180</v>
       </c>
       <c r="R14" t="n">
-        <v>-393000</v>
+        <v>50000</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>109000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 호조에도 불구하고 주가 하락 및 부정적 전망이 지배적. 외인 매도세 및 급락 가능성에 대한 우려 제기.</t>
+          <t>해외 수출 및 신약 개발 관련 긍정적 전망. AI 신약 개발 활용 및 성장성 확장성 확고. 공매도 숏커버링 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적', '주가 하락', '외인 매도']</t>
+          <t>['AI 신약 개발', '수출', '성장성']</t>
         </is>
       </c>
       <c r="X14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>328130</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>34450</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-5.62%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E15" t="n">
+        <v>146</v>
+      </c>
+      <c r="F15" t="n">
+        <v>94</v>
+      </c>
+      <c r="G15" t="n">
+        <v>242</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>36500</v>
+      </c>
+      <c r="K15" t="n">
+        <v>38750</v>
+      </c>
+      <c r="L15" t="n">
+        <v>42150</v>
+      </c>
+      <c r="M15" t="n">
+        <v>33550</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="O15" t="n">
+        <v>109084705200</v>
+      </c>
+      <c r="P15" t="n">
+        <v>126600</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>15260</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-393000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>실적 부진 및 하한가 기록. 광통신 업종 전반의 약세와 수급 불안정성 언급. 금감원 규제 촉구.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['실적 부진', '하한가', '광통신']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
         <v>1</v>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>327260</t>
         </is>
